--- a/D2_Measure/Findings/D2_Measure_Findings_Bottling.xlsx
+++ b/D2_Measure/Findings/D2_Measure_Findings_Bottling.xlsx
@@ -32,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +74,14 @@
       <color rgb="007B1FA2"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00546E7A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -94,7 +100,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000BCD4"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,6 +111,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B5E20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,11 +193,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -185,35 +209,53 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -297,7 +339,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -327,7 +369,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -357,7 +399,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -387,7 +429,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -417,7 +459,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -447,7 +489,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -477,7 +519,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -507,7 +549,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -537,7 +579,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -567,7 +609,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -597,7 +639,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -627,7 +669,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -657,7 +699,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -687,7 +729,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -717,7 +759,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -747,7 +789,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8639937" cy="5039963"/>
@@ -1060,162 +1102,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B41"/>
+  <dimension ref="B1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Measure Phase — KPI Dashboard</t>
+          <t>Measure Phase — KPI Dashboard — Executive Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>📈 Chart: KPI Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — KPI Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>📈  Chart: KPI Dashboard — Executive Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>📊  Findings — KPI Dashboard — Executive Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The overall defect rate stands at 4.49%, which is 3.49 percentage points above the 1% target — a critical gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The current Sigma Level is 3.2σ with a DPMO of 44,896, far from the 4.5σ (DPMO ≤ 1,350) target.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • On-time delivery is only 79.9% against a 95% target, indicating significant fulfillment delays.</t>
+          <t xml:space="preserve">  •  Defect rate is 4.49% — 3.49 pts above the 1% target.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Average changeover time is 44.8 minutes — more than double the 20-minute target.</t>
+          <t xml:space="preserve">  •  Sigma Level = 3.2σ | DPMO = 44,896 — far from the 4.5σ target.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Unplanned downtime accounts for 55.3% of all downtime, well above the 20% threshold.</t>
+          <t xml:space="preserve">  •  On-time delivery = 79.9% vs. 95% target — critical gap.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Customer satisfaction (CSAT) is 3.40/5, below the 4.0/5 target, reflecting the impact of quality and delivery issues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Average changeover = 44.8 min — more than double the 20-min target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Unplanned downtime = 55.3% of all downtime (target ≤20%).</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>معدل العيوب الإجمالي يبلغ 4.49%، أي أعلى من الهدف (1%) بفارق 3.49 نقطة مئوية — فجوة حرجة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>مستوى سيجما الحالي 3.2σ مع DPMO = 44,896، بعيد جداً عن الهدف 4.5σ (DPMO ≤ 1,350).  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>نسبة التسليم في الوقت المحدد 79.9% فقط مقابل هدف 95%، مما يشير إلى تأخيرات جوهرية في التوصيل.  •</t>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  CSAT = 3.40/5 — below the 4.0/5 target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1">
+      <c r="B37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>متوسط وقت التحويل 44.8 دقيقة — أكثر من ضعف الهدف المحدد بـ 20 دقيقة.  •</t>
+          <t>معدل العيوب 4.49% — أعلى من الهدف (1%) بـ 3.49 نقطة.  •</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>التوقف غير المخطط يمثل 55.3% من إجمالي التوقف، أعلى بكثير من حد 20%.  •</t>
+          <t>مستوى سيجما = 3.2σ | DPMO = 44,896 — بعيد عن هدف 4.5σ.  •</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>رضا العملاء (CSAT) 3.40/5، أقل من الهدف 4.0/5، مما يعكس تأثير مشاكل الجودة والتسليم.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="8" customHeight="1"/>
+          <t>التسليم في الوقت = 79.9% مقابل هدف 95% — فجوة حرجة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>متوسط التحويل = 44.8 دق — أكثر من ضعف هدف 20 دقيقة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>التوقف غير المخطط = 55.3% من إجمالي التوقف (الهدف ≤20%).  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>رضا العملاء = 3.40/5 — أقل من الهدف 4.0/5.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="6" customHeight="1">
+      <c r="B45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A KPI Dashboard is a single-view summary of the most critical process metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: It gives decision-makers an instant snapshot of process health without diving into raw data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Each KPI shows the current value vs. target. Red = failing, Green = on track.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Used in the Measure phase to establish the baseline and quantify the problem size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: When multiple KPIs are all in the red simultaneously, it signals a systemic process failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="6" customHeight="1">
+      <c r="B53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open the dataset sheet (e.g., "4-Defect &amp; Quality") in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Calculate each KPI using formulas: =AVERAGE(), =COUNTIF(), =SUM() as needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Create a summary table with columns: KPI | Current Value | Target | Status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. For the Status column, use: =IF(B2&lt;=C2,"✅ On Track","🔴 Off Target")</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Select the KPI values → Insert → Bar Chart (Clustered) to compare current vs. target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add a secondary axis for percentage-based KPIs vs. count-based KPIs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Format: color bars red/green based on target achievement using conditional formatting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Add data labels: Right-click chart → Add Data Labels → Show Value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="6" customHeight="1">
+      <c r="B64" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B40"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1227,146 +1408,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>Measure Phase — Changeover Analysis</t>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Measure Phase — Changeover Time Analysis</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>📈 Chart: Changeover Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Changeover Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>📈  Chart: Changeover Time Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>📊  Findings — Changeover Time Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • 100.0% of all changeovers exceed the 20-minute target — virtually all changeovers are non-compliant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The average changeover time is 44.8 minutes, which is 24.8 minutes above target.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The "330ml" SKU transition has the longest average changeover at 45.1 minutes.</t>
+          <t xml:space="preserve">  •  100.0% of all changeovers exceed the 20-minute target.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Excessive changeover times directly reduce available production time and contribute to schedule non-adherence.</t>
+          <t xml:space="preserve">  •  Average changeover = 44.8 min — 24.8 min above target.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Applying SMED (Single-Minute Exchange of Die) methodology is strongly recommended to reduce changeover time to ≤20 minutes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  "330ml" SKU transition has the longest average: 45.1 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Excessive changeover times reduce available production time and cause schedule delays.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>100.0% من جميع عمليات التحويل تتجاوز هدف 20 دقيقة — تقريباً جميع عمليات التحويل غير متوافقة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>متوسط وقت التحويل 44.8 دقيقة، أي أعلى من الهدف بـ 24.8 دقيقة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>انتقال حجم "330ml" لديه أطول متوسط تحويل بـ 45.1 دقيقة.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  SMED (Single-Minute Exchange of Die) methodology is recommended to reach ≤20 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>أوقات التحويل المفرطة تُقلل مباشرة من وقت الإنتاج المتاح وتُسهم في عدم الالتزام بالجدول الزمني.  •</t>
+          <t>100.0% من جميع عمليات التحويل تتجاوز هدف 20 دقيقة.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>يُوصى بشدة بتطبيق منهجية SMED (تبادل القالب في دقيقة واحدة) لتقليل وقت التحويل إلى ≤20 دقيقة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>متوسط التحويل = 44.8 دق — أعلى من الهدف بـ 24.8 دقيقة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>انتقال "330ml" لديه أطول متوسط: 45.1 دقيقة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>أوقات التحويل المفرطة تُقلل وقت الإنتاج المتاح وتُسبب تأخيرات في الجدول.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يُوصى بتطبيق منهجية SMED للوصول إلى ≤20 دقيقة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A histogram or scatter plot showing the distribution of changeover times vs. the 20-min target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Changeover time is a major source of production loss — reducing it increases capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Each data point is one changeover event. Points above the red line exceed the target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Changeover time is a key input variable (X) affecting output (Y = production output).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: If most changeovers exceed the target, the issue is the process design, not individual operators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "3-Changeover Times" → review columns: From SKU, To SKU, Duration (min), Target (min).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Add a helper column: =IF(D2&gt;E2,"Over Target","On Target") to flag violations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Create a summary by SKU transition: average duration per From→To SKU pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. For a histogram: select Duration column → Insert → Statistical Chart → Histogram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. For a scatter plot: select Date + Duration → Insert → Scatter Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add a horizontal reference line at 20 min (target) as a constant series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Color points/bars: red if &gt;20 min, green if ≤20 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Add title: "Changeover Duration vs. 20-Minute Target".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1378,146 +1700,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Measure Phase — Production Actual vs Planned</t>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Measure Phase — Production Actual vs. Planned Output</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>📈 Chart: Production Actual vs Planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Production Actual vs Planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>📈  Chart: Production Actual vs. Planned Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>📊  Findings — Production Actual vs. Planned Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Total actual output was 28,422,020 bottles vs. planned 32,206,042 bottles — a gap of 3,784,022 bottles (11.7% shortfall).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Average schedule adherence is 88.2%, which is below the 90% target.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Monthly production gaps are driven by unplanned downtime, excessive changeover times, and quality-related stoppages.</t>
+          <t xml:space="preserve">  •  Total actual: 28,422,020 bottles vs. planned 32,206,042 — gap of 3,784,022 bottles.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Consistent output shortfalls impact order fulfillment and on-time delivery performance.</t>
+          <t xml:space="preserve">  •  Output gap = 11.7% shortfall.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Stabilizing the production process through downtime and changeover reduction will directly improve output adherence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Average schedule adherence = 88.2% (target ≥90%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Monthly gaps are driven by unplanned downtime, changeover delays, and quality stoppages.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>الإنتاج الفعلي الإجمالي 28,422,020 زجاجة مقابل المخطط 32,206,042 — فجوة 3,784,022 زجاجة (11.7% عجز).  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>متوسط الالتزام بالجدول 88.2%، وهو أقل من هدف 90%.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>فجوات الإنتاج الشهرية مدفوعة بالتوقف غير المخطط وأوقات التحويل المفرطة والتوقفات المرتبطة بالجودة.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Stabilizing the process will directly improve output adherence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>العجز المستمر في الإنتاج يؤثر على تنفيذ الطلبات وأداء التسليم في الوقت المحدد.  •</t>
+          <t>الإنتاج الفعلي: 28,422,020 زجاجة مقابل المخطط 32,206,042 — فجوة 3,784,022 زجاجة.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>استقرار عملية الإنتاج من خلال تقليل التوقف والتحويل سيُحسّن مباشرة الالتزام بالإنتاج.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>فجوة الإنتاج = 11.7% عجز.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>متوسط الالتزام بالجدول = 88.2% (الهدف ≥90%).  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>الفجوات الشهرية مدفوعة بالتوقف غير المخطط وتأخيرات التحويل والتوقفات المرتبطة بالجودة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>استقرار العملية سيُحسّن مباشرة الالتزام بالإنتاج.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A grouped bar chart comparing actual vs. planned production output month by month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Reveals the production gap — how much output is being lost due to process problems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Blue bars = planned. Orange bars = actual. Gap between them = lost production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Quantifies the business impact of process inefficiencies in financial/volume terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: Consistent actual &lt; planned means the process cannot sustain its design capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "1-Production Output" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = Month | Values = SUM(Actual Output) and SUM(Planned Output).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Copy results to a clean table: Month | Planned | Actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select all 3 columns → Insert → Clustered Column Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. The chart will show 2 bars per month — planned (blue) and actual (orange).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add a line series for Schedule Adherence % on a secondary axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add data labels and a reference line at 90% adherence target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Monthly Production: Actual vs. Planned Output".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1529,146 +1992,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Measure Phase — Fulfillment &amp; On-Time Delivery</t>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Measure Phase — Fulfillment Rate &amp; On-Time Delivery</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>📈 Chart: Fulfillment &amp; On-Time Delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Fulfillment &amp; On-Time Delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>📈  Chart: Fulfillment Rate &amp; On-Time Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>📊  Findings — Fulfillment Rate &amp; On-Time Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • While fulfillment rate averages 100.0% (meeting the ≥95% target), on-time delivery is only 79.9% — far below the 95% target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • There were 0 stockout events and 0 partial deliveries recorded over the 6-month period.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The "1.5L" SKU has the lowest fulfillment rate at 100.0%, indicating SKU-specific supply chain issues.</t>
+          <t xml:space="preserve">  •  Fulfillment rate avg = 100.0% (meets ≥95% target) but on-time delivery = 79.9%.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The gap between fulfillment rate and on-time delivery suggests orders are being fulfilled but with delays.</t>
+          <t xml:space="preserve">  •  0 stockout events and 0 partial deliveries in 6 months.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Reducing production downtime and improving scheduling will directly improve on-time delivery performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  "1.5L" SKU has the lowest fulfillment rate: 100.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Orders are being fulfilled but with delays — scheduling is the root issue.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>بينما يبلغ متوسط معدل التنفيذ 100.0% (يحقق هدف ≥95%)، فإن التسليم في الوقت المحدد 79.9% فقط — أقل بكثير من هدف 95%.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>سُجّلت 0 حالة نفاد مخزون و0 توصيل جزئي خلال فترة 6 أشهر.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>حجم "1.5L" لديه أدنى معدل تنفيذ بـ 100.0%، مما يشير إلى مشاكل سلسلة توريد خاصة بهذا الحجم.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Reducing downtime and improving scheduling will directly improve on-time delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>الفجوة بين معدل التنفيذ والتسليم في الوقت المحدد تشير إلى أن الطلبات تُنفَّذ لكن مع تأخيرات.  •</t>
+          <t>متوسط معدل التنفيذ = 100.0% (يحقق هدف ≥95%) لكن التسليم في الوقت = 79.9%.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>تقليل توقف الإنتاج وتحسين الجدولة سيُحسّن مباشرة أداء التسليم في الوقت المحدد.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>0 حالة نفاد مخزون و0 توصيل جزئي خلال 6 أشهر.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>حجم "1.5L" لديه أدنى معدل تنفيذ: 100.0%.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>الطلبات تُنفَّذ لكن مع تأخيرات — الجدولة هي السبب الجذري.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>تقليل التوقف وتحسين الجدولة سيُحسّن مباشرة التسليم في الوقت المحدد.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A dual-axis chart showing fulfillment rate (bars) and on-time delivery % (line) per month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Distinguishes between whether orders are completed (fulfillment) vs. completed on time (delivery).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: High fulfillment + low on-time = orders are done but late. Both low = capacity problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Connects production performance to customer-facing outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: A gap between fulfillment and on-time delivery points to scheduling/planning failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "6-Inventory &amp; Fulfillment" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = Month | Values = AVERAGE(Fulfillment Rate %) and COUNTIF(On-Time Delivery,"Yes")/COUNT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Copy to a clean table: Month | Fulfillment Rate | On-Time Delivery %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select all columns → Insert → Clustered Column Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Right-click the On-Time Delivery series → Change Chart Type → Line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add secondary axis for the line series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add reference lines at 95% for both metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Monthly Fulfillment Rate vs. On-Time Delivery %".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1680,146 +2284,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="17" t="inlineStr">
-        <is>
-          <t>Measure Phase — Pareto: Customer Complaints</t>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Measure Phase — Pareto Chart — Customer Complaints</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>📈 Chart: Pareto: Customer Complaints</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Pareto: Customer Complaints</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>📈  Chart: Pareto Chart — Customer Complaints</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>📊  Findings — Pareto Chart — Customer Complaints</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The top complaint type is "Leaking bottles" accounting for 25.7% of all affected units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The second complaint type is "Late delivery" at 19.8% of total complaint volume.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Customer complaints are directly linked to the defect types identified in the quality analysis — confirming the voice of the customer.</t>
+          <t xml:space="preserve">  •  Top complaint: "Leaking bottles" = 25.7% of affected units.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Resolving the top 2 complaint types would address the majority of customer dissatisfaction.</t>
+          <t xml:space="preserve">  •  2nd complaint: "Late delivery" = 19.8% of total complaint volume.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Complaint data should be cross-referenced with defect station and shift data to identify the root cause chain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Complaints directly mirror the defect types found in quality analysis — VoC confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Resolving top 2 complaint types would address the majority of customer dissatisfaction.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>أكثر أنواع الشكاوى شيوعاً هو "Leaking bottles" بنسبة 25.7% من إجمالي الوحدات المتأثرة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>النوع الثاني "Late delivery" بنسبة 19.8% من إجمالي حجم الشكاوى.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>شكاوى العملاء مرتبطة مباشرة بأنواع العيوب المحددة في تحليل الجودة — مما يؤكد صوت العميل.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Cross-reference complaints with station and shift data to identify the root cause chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>حل أعلى نوعين من الشكاوى سيعالج غالبية عدم رضا العملاء.  •</t>
+          <t>أكثر الشكاوى: "Leaking bottles" = 25.7% من الوحدات المتأثرة.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>يجب مقارنة بيانات الشكاوى مع بيانات محطة العيوب والوردية لتحديد سلسلة السبب الجذري.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>الشكوى الثانية: "Late delivery" = 19.8% من إجمالي حجم الشكاوى.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>الشكاوى تعكس مباشرة أنواع العيوب الموجودة في تحليل الجودة — صوت العميل مؤكد.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>حل أعلى نوعين من الشكاوى سيعالج غالبية عدم رضا العملاء.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>قارن الشكاوى مع بيانات المحطة والوردية لتحديد سلسلة السبب الجذري.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A Pareto chart of customer complaint types sorted by volume of affected units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Connects internal quality data to external customer experience — the Voice of the Customer (VoC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Bars = complaint volume. Line = cumulative %. Focus on the first 2-3 bars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Validates that internal defects are causing real customer impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: If complaint types match defect types, the measurement system is aligned with customer needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "7-Customer Complaints" → create a summary: Complaint Type | Quantity Affected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Use SUMIF to aggregate by complaint type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Sort by Quantity Affected descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Add Cumulative % column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Select Complaint Type + Quantity → Insert → Clustered Bar Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add Cumulative % as a Line on Secondary Axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add 80% reference line on secondary axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Format and title: "Pareto Analysis — Customer Complaint Types".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1831,146 +2576,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="17" t="inlineStr">
-        <is>
-          <t>Measure Phase — CSAT Monthly Trend</t>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Measure Phase — Customer Satisfaction (CSAT) Monthly Trend</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>📈 Chart: CSAT Monthly Trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — CSAT Monthly Trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>📈  Chart: Customer Satisfaction (CSAT) Monthly Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>📊  Findings — Customer Satisfaction (CSAT) Monthly Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Average CSAT is 3.40/5, which is 0.60 points below the 4.0/5 target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Only 53.2% of customers rated their experience 4 or above, indicating widespread dissatisfaction.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The worst CSAT month was 2026-03 with an average score of 3.33/5.</t>
+          <t xml:space="preserve">  •  Average CSAT = 3.40/5 — 0.60 pts below the 4.0/5 target.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The best CSAT month was 2025-12 with an average score of 3.46/5 — still below target.</t>
+          <t xml:space="preserve">  •  Only 53.2% of customers rated 4 or above — widespread dissatisfaction.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • CSAT improvement is directly dependent on resolving defect, delivery, and complaint issues identified in this Measure phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Worst CSAT month: 2026-03 at 3.33/5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Best CSAT month: 2025-12 at 3.46/5 — still below target.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>متوسط رضا العملاء 3.40/5، أي أقل من الهدف 4.0/5 بفارق 0.60 نقطة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>53.2% فقط من العملاء قيّموا تجربتهم بـ 4 أو أعلى، مما يدل على عدم رضا واسع النطاق.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>أسوأ شهر من حيث رضا العملاء كان 2026-03 بمتوسط درجة 3.33/5.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  CSAT improvement depends on resolving defect, delivery, and complaint issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>أفضل شهر كان 2025-12 بمتوسط درجة 3.46/5 — لا يزال أقل من الهدف.  •</t>
+          <t>متوسط رضا العملاء = 3.40/5 — أقل من الهدف 4.0/5 بـ 0.60 نقطة.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>تحسين رضا العملاء يعتمد مباشرة على حل مشاكل العيوب والتسليم والشكاوى المحددة في مرحلة القياس هذه.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>53.2% فقط من العملاء قيّموا بـ 4 أو أعلى — عدم رضا واسع النطاق.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>أسوأ شهر: 2026-03 بمتوسط 3.33/5.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>أفضل شهر: 2025-12 بمتوسط 3.46/5 — لا يزال أقل من الهدف.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>تحسين رضا العملاء يعتمد على حل مشاكل العيوب والتسليم والشكاوى.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A line chart tracking average customer satisfaction score (1-5) month by month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: CSAT is the ultimate output metric — it reflects the cumulative impact of all process problems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Higher line = better satisfaction. The dashed line marks the 4.0/5 target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: CSAT is the Y (output) variable that all X (input) improvements should ultimately improve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: CSAT trends that mirror defect/delivery trends confirm the cause-effect relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "7-Customer Complaints" → add a helper column: =TEXT(Date,"YYYY-MM") for month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Create a Pivot Table: Rows = Month | Values = AVERAGE(Customer Satisfaction Score).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Copy to a clean table: Month | Avg CSAT | Target (4.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select Month + Avg CSAT → Insert → Line Chart with Markers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Add Target as a constant series (value = 4.0 for all months) → format as dashed line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Set Y-axis range from 1 to 5 to show the full scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add data labels on each marker point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Monthly Customer Satisfaction Score (CSAT) Trend".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1982,146 +2868,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Measure Phase — Sigma Level &amp; DPMO</t>
+          <t>Measure Phase — Sigma Level &amp; DPMO Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>📈 Chart: Sigma Level &amp; DPMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Sigma Level &amp; DPMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>📈  Chart: Sigma Level &amp; DPMO Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>📊  Findings — Sigma Level &amp; DPMO Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The current process operates at 3.2σ with a DPMO of 44,896 — classified as a 3σ process.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • To reach the 4.5σ target, the DPMO must be reduced from 44,896 to ≤1,350 — a 33x improvement required.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • At 3σ, approximately 4.5% of all output contains defects — unacceptable for a food/beverage production environment.</t>
+          <t xml:space="preserve">  •  Current process: 3.2σ | DPMO = 44,896 — classified as a 3σ process.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The gap from current sigma to target (4.5σ) represents a significant process capability improvement challenge.</t>
+          <t xml:space="preserve">  •  To reach 4.5σ target: DPMO must drop from 44,896 to ≤1,350 — a 33x improvement needed.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Achieving 4.5σ will require systematic elimination of the top defect causes identified in this Measure phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  At 3.2σ, ~4.5% of all output contains defects — unacceptable for food/beverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  The sigma gap represents a significant process capability improvement challenge.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>العملية الحالية تعمل عند 3.2σ مع DPMO = 44,896 — مصنّفة كعملية 3σ.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>للوصول إلى هدف 4.5σ، يجب تقليل DPMO من 44,896 إلى ≤1,350 — مطلوب تحسين بمقدار 33 مرة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>عند 3σ، تقريباً 4.5% من الإنتاج يحتوي على عيوب — غير مقبول في بيئة إنتاج الأغذية والمشروبات.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Systematic elimination of top defect causes is required to achieve 4.5σ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>الفجوة من سيجما الحالية إلى الهدف (4.5σ) تمثل تحدياً كبيراً لتحسين قدرة العملية.  •</t>
+          <t>العملية الحالية: 3.2σ | DPMO = 44,896 — مصنّفة كعملية 3σ.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>تحقيق 4.5σ يتطلب القضاء المنهجي على أسباب العيوب الرئيسية المحددة في مرحلة القياس هذه.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>للوصول إلى 4.5σ: يجب تقليل DPMO من 44,896 إلى ≤1,350 — مطلوب تحسين بمقدار 33 مرة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>عند 3.2σ، ~4.5% من الإنتاج يحتوي على عيوب — غير مقبول في صناعة الأغذية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>فجوة سيجما تمثل تحدياً كبيراً لتحسين قدرة العملية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>القضاء المنهجي على أسباب العيوب الرئيسية مطلوب لتحقيق 4.5σ.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A gauge/bar chart showing the current Sigma Level vs. the target, with DPMO context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Sigma Level is the universal Six Sigma metric that quantifies overall process quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Higher sigma = better quality. 6σ = 3.4 DPMO (near-perfect). 3σ = 66,807 DPMO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: The Sigma Level is the primary baseline metric established in the Measure phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: Moving from 3σ to 4.5σ is not incremental — it requires fundamental process redesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Calculate DPMO: = (Total Defective Units / Total Produced Units) * 1,000,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Calculate Sigma Level using the formula: =NORM.S.INV(1-DPMO/1000000)+1.5 in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Create a comparison table: Sigma Level | DPMO | Defect Rate % | Status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Add rows for: Current, Target (4.5σ), World Class (6σ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Create a horizontal bar chart: Sigma levels on Y-axis, value on X-axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Color current bar red, target bar green, world class bar gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add a vertical reference line at the target sigma level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Process Sigma Level: Current vs. Target vs. World Class".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2133,16 +3160,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Measure Phase — MTBF &amp; MTTR by Machine</t>
         </is>
@@ -2151,128 +3178,269 @@
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>📈 Chart: MTBF &amp; MTTR by Machine</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — MTBF &amp; MTTR by Machine</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>📈  Chart: MTBF &amp; MTTR by Machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>📊  Findings — MTBF &amp; MTTR by Machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "Labeling Machine" machine has the lowest MTBF at 100.2 hours — the least reliable machine on the line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "Conveyor System" machine has the highest MTBF at 120.3 hours — the most reliable machine.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • 21.0% of maintenance work orders have pending issues, indicating unresolved equipment problems.</t>
+          <t xml:space="preserve">  •  "Labeling Machine" machine: lowest MTBF = 100.2 hrs — least reliable.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The ratio of corrective to preventive maintenance (1175:1123) confirms a reactive maintenance culture.</t>
+          <t xml:space="preserve">  •  "Conveyor System" machine: highest MTBF = 120.3 hrs — most reliable.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Improving MTBF through better PM scheduling and spare parts management will directly reduce unplanned downtime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  21.0% of maintenance work orders have pending issues — unresolved equipment problems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Corrective vs. Preventive ratio: 1175:1123 — reactive maintenance culture.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>آلة "Labeling Machine" لديها أدنى MTBF بـ 100.2 ساعة — الآلة الأقل موثوقية في الخط.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>آلة "Conveyor System" لديها أعلى MTBF بـ 120.3 ساعة — الآلة الأكثر موثوقية.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>21.0% من أوامر الصيانة لديها مشاكل معلقة، مما يشير إلى مشاكل معدات لم تُحل.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Improving PM scheduling and spare parts management will reduce unplanned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>نسبة الصيانة التصحيحية إلى الوقائية (1175:1123) تؤكد ثقافة الصيانة التفاعلية.  •</t>
+          <t>آلة "Labeling Machine": أدنى MTBF = 100.2 ساعة — الأقل موثوقية.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>تحسين MTBF من خلال جدولة أفضل للصيانة الوقائية وإدارة قطع الغيار سيُقلل مباشرة من التوقف غير المخطط.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>آلة "Conveyor System": أعلى MTBF = 120.3 ساعة — الأكثر موثوقية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>21.0% من أوامر الصيانة لديها مشاكل معلقة — مشاكل معدات لم تُحل.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>نسبة التصحيحية إلى الوقائية: 1175:1123 — ثقافة صيانة تفاعلية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>تحسين جدولة الصيانة الوقائية وإدارة قطع الغيار سيُقلل التوقف غير المخطط.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A grouped bar chart showing MTBF (Mean Time Between Failures) and MTTR (Mean Time To Repair) per machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: MTBF measures reliability (how long before failure). MTTR measures maintainability (how fast to fix).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Higher MTBF = more reliable. Lower MTTR = faster repair. Best machine = high MTBF + low MTTR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Maintenance KPIs are key input variables (X) affecting production uptime (Y).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: A machine with low MTBF AND high MTTR is the highest-risk asset on the production line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "5-Maintenance Logs" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = Machine | Values = AVERAGE(MTBF (hrs)) and AVERAGE(MTTR (hrs)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Copy to a clean table: Machine | Avg MTBF | Avg MTTR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select Machine + MTBF + MTTR → Insert → Clustered Bar Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. MTBF and MTTR will appear as two bars per machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add a secondary axis for MTTR if the scales are very different.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Color MTBF bars blue (higher = better), MTTR bars orange (lower = better).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Machine Reliability: MTBF &amp; MTTR by Machine".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2284,146 +3452,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Measure Phase — Monthly Defect Trend</t>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Measure Phase — Monthly Defect Rate Trend</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>📈 Chart: Monthly Defect Trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Monthly Defect Trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>📈  Chart: Monthly Defect Rate Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>📊  Findings — Monthly Defect Rate Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Defect rates ranged from 4.38% (best: 2026-01) to 4.62% (worst: 2025-12) over the 6-month period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • No month achieved the 1% defect rate target — the process is consistently out of control.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The trend shows high variation month-to-month, indicating the process lacks stability and predictability.</t>
+          <t xml:space="preserve">  •  Defect rates ranged from 4.38% to 4.62% over 6 months.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The worst month (2025-12) had a defect rate of 4.62%, which is 3.62x the target.</t>
+          <t xml:space="preserve">  •  No month achieved the 1% target — process is consistently out of control.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • This persistent elevation above target confirms that the defect problem is systemic, not a one-time occurrence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Worst month: 2025-12 at 4.62% | Best month: 2026-01 at 4.38%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  High month-to-month variation indicates process instability.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>تراوحت معدلات العيوب بين 4.38% (الأفضل: 2026-01) و4.62% (الأسوأ: 2025-12) خلال 6 أشهر.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>لم يحقق أي شهر هدف معدل العيوب 1% — العملية خارجة عن السيطرة باستمرار.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>يُظهر الاتجاه تذبذباً كبيراً من شهر لآخر، مما يدل على افتقار العملية للاستقرار والقدرة على التنبؤ.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  The persistent elevation above target confirms a systemic, not random, problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>أسوأ شهر (2025-12) سجّل معدل عيوب 4.62%، أي 3.62 مرة فوق الهدف.  •</t>
+          <t>تراوحت معدلات العيوب بين 4.38% و4.62% خلال 6 أشهر.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>هذا الارتفاع المستمر فوق الهدف يؤكد أن مشكلة العيوب منهجية وليست حادثة عرضية.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>لم يحقق أي شهر هدف 1% — العملية خارجة عن السيطرة باستمرار.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>أسوأ شهر: 2025-12 بـ 4.62% | أفضل شهر: 2026-01 بـ 4.38%.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>التذبذب الشهري الكبير يدل على عدم استقرار العملية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>الارتفاع المستمر فوق الهدف يؤكد أن المشكلة منهجية وليست عشوائية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A line chart showing how the defect rate changes month by month over 6 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Trend analysis reveals whether the process is improving, worsening, or stable over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: The red dashed line is the 1% target. Any point above it is a failing month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Used to assess process stability (control) before deeper analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: A flat trend above target means the problem is structural — not seasonal or random.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open sheet "4-Defect &amp; Quality" in Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Add a helper column: =TEXT(A2,"YYYY-MM") to extract the month from the Date column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Create a Pivot Table: Rows = Month | Values = SUM(Units Defective) and SUM(Units Produced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Add a calculated field: Defect Rate = Units Defective / Units Produced * 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Copy the pivot results to a new table with columns: Month | Defect Rate (%) | Target (1%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Select both columns → Insert → Line Chart → Line with Markers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add a constant target line: right-click chart → Select Data → Add series with value 1 for all months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Format the target line as dashed red. Add chart title and axis labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2435,146 +3744,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Measure Phase — Pareto: Defect Types</t>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Measure Phase — Pareto Chart — Defect Types</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>📈 Chart: Pareto: Defect Types</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Pareto: Defect Types</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>📈  Chart: Pareto Chart — Defect Types</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>📊  Findings — Pareto Chart — Defect Types</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The top defect type is "Leakage" accounting for 26.1% of all defective units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The second defect type is "Poor sealing" at 19.3%, and third is "Label misalignment" at 14.6%.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The top 3 defect types together account for 59.9% of all defects — confirming the 80/20 Pareto principle.</t>
+          <t xml:space="preserve">  •  Top defect: "Leakage" = 26.1% of all defective units.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Focusing improvement efforts on these 3 defect types alone could eliminate ~60% of all quality losses.</t>
+          <t xml:space="preserve">  •  2nd: "Poor sealing" = 19.3% | 3rd: "Label misalignment" = 14.6%.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • This Pareto analysis provides clear prioritization for the root cause analysis in the Analyze phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Top 3 defect types = 59.9% of all defects — confirms 80/20 Pareto rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Fixing these 3 types alone could eliminate ~60% of quality losses.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>أكثر أنواع العيوب شيوعاً هو "Leakage" بنسبة 26.1% من إجمالي الوحدات المعيبة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>النوع الثاني "Poor sealing" بنسبة 19.3%، والثالث "Label misalignment" بنسبة 14.6%.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>أعلى 3 أنواع من العيوب تمثل معاً 59.9% من جميع العيوب — مما يؤكد مبدأ باريتو 80/20.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  This analysis provides clear prioritization for root cause investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>التركيز على هذه الأنواع الثلاثة وحدها يمكن أن يُزيل ~60% من جميع خسائر الجودة.  •</t>
+          <t>أكثر العيوب: "Leakage" = 26.1% من الوحدات المعيبة.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>يوفر تحليل باريتو هذا أولويات واضحة لتحليل السبب الجذري في مرحلة التحليل.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>الثاني: "Poor sealing" = 19.3% | الثالث: "Label misalignment" = 14.6%.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>أعلى 3 أنواع = 59.9% من جميع العيوب — يؤكد قاعدة باريتو 80/20.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>إصلاح هذه الأنواع الثلاثة وحدها يمكن أن يُزيل ~60% من خسائر الجودة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يوفر هذا التحليل أولويات واضحة لتحقيق السبب الجذري.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A Pareto chart combines a bar chart (frequency) with a cumulative line chart (%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: It visually identifies the "vital few" causes responsible for the majority of defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Bars are sorted from highest to lowest. The line shows cumulative % reaching 80%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Core tool in the Measure phase to prioritize which defects to investigate first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: Focus improvement efforts on the first 2-3 bars to get the maximum quality gain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "4-Defect &amp; Quality" → create a summary: Defect Type | Count | % of Total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Sort the table by Count descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Add a Cumulative % column: =SUM($B$2:B2)/SUM($B$2:$B$10)*100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select Defect Type + Count columns → Insert → Clustered Bar Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Right-click chart → Select Data → Add a second series for Cumulative %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Right-click the Cumulative % series → Change Series Chart Type → Line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Right-click the line → Format Data Series → Secondary Axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Add a horizontal reference line at 80% on the secondary axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9. Format: bars in descending color gradient, line in orange, add data labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="6" customHeight="1">
+      <c r="B63" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2586,16 +4043,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Measure Phase — Defect Rate by Shift</t>
         </is>
@@ -2604,128 +4061,269 @@
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>📈 Chart: Defect Rate by Shift</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Defect Rate by Shift</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>📈  Chart: Defect Rate by Shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>📊  Findings — Defect Rate by Shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "Night (23-07)" shift has the highest defect rate at 4.54%, significantly above the overall average.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "Morning (07-15)" shift performs best with a defect rate of 4.45%.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The gap between the worst and best shift is 0.09 percentage points — a significant variation.</t>
+          <t xml:space="preserve">  •  "Night (23-07)" shift has the highest defect rate: 4.54%.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • This shift-based variation suggests that human factors, supervision levels, and fatigue play a key role in defect generation.</t>
+          <t xml:space="preserve">  •  "Morning (07-15)" shift is the best performer: 4.45%.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Standardizing work procedures and improving night shift supervision should be prioritized in the Improve phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Gap between worst and best shift: 0.09 percentage points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Shift variation suggests human factors and supervision levels drive defects.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>وردية "Night (23-07)" لديها أعلى معدل عيوب بنسبة 4.54%، أعلى بشكل ملحوظ من المتوسط العام.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>وردية "Morning (07-15)" هي الأفضل أداءً بمعدل عيوب 4.45%.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>الفجوة بين أسوأ وأفضل وردية 0.09 نقطة مئوية — تباين كبير.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Standardizing procedures and improving night shift oversight is recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>يشير هذا التباين بين الورديات إلى أن العوامل البشرية ومستويات الإشراف والإجهاد تلعب دوراً رئيسياً في توليد العيوب.  •</t>
+          <t>وردية "Night (23-07)" لديها أعلى معدل عيوب: 4.54%.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ينبغي إعطاء الأولوية لتوحيد إجراءات العمل وتحسين إشراف الوردية الليلية في مرحلة التحسين.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>وردية "Morning (07-15)" هي الأفضل أداءً: 4.45%.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>الفجوة بين أسوأ وأفضل وردية: 0.09 نقطة مئوية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>التباين بين الورديات يشير إلى أن العوامل البشرية ومستوى الإشراف يقودان العيوب.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يُوصى بتوحيد الإجراءات وتحسين إشراف الوردية الليلية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A grouped bar chart comparing the defect rate across Morning, Afternoon, and Night shifts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Shift-based stratification reveals whether human factors (fatigue, training) affect quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Each bar represents one shift. Higher bar = more defects in that shift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Stratification by shift is a key step in identifying special-cause variation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: If one shift consistently outperforms others, its practices should be standardized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "4-Defect &amp; Quality" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = Shift | Values = SUM(Units Defective) and SUM(Units Produced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. In a new table, calculate: Defect Rate (%) = Defective / Produced * 100 for each shift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select Shift + Defect Rate → Insert → Clustered Column Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Add a reference line at the overall average: Insert → Shapes → Line, or add a constant series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add data labels: Right-click → Add Data Labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Color code: red for shifts above average, green for below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Add chart title: "Defect Rate by Shift" and label the Y-axis as "Defect Rate (%)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2737,146 +4335,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Measure Phase — Defect Rate by Station</t>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Measure Phase — Defect Rate by Production Station</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>📈 Chart: Defect Rate by Station</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Defect Rate by Station</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>📈  Chart: Defect Rate by Production Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>📊  Findings — Defect Rate by Production Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "Capping" station has the highest defect rate at 4.54%, making it the critical bottleneck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • This station should be the primary focus for root cause investigation in the Analyze phase.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Defect rates vary significantly across stations, indicating that station-specific factors (machine condition, operator skill) drive quality issues.</t>
+          <t xml:space="preserve">  •  "Capping" station has the highest defect rate: 4.54%.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Stations with lower defect rates can serve as benchmarks for best practices to be replicated across the line.</t>
+          <t xml:space="preserve">  •  Station-level variation confirms machine condition and operator skill are key factors.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • A deeper process mapping of the Capping station is recommended to identify specific failure modes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Low-defect stations can serve as benchmarks for best practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Focusing on Capping station is the highest-impact improvement opportunity.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>محطة "Capping" لديها أعلى معدل عيوب بنسبة 4.54%، مما يجعلها الاختناق الحرج.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>يجب أن تكون هذه المحطة المحور الرئيسي لتحقيق السبب الجذري في مرحلة التحليل.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>تتباين معدلات العيوب بشكل ملحوظ عبر المحطات، مما يشير إلى أن عوامل خاصة بكل محطة (حالة الآلة، مهارة المشغّل) تقود مشاكل الجودة.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Detailed process mapping of the worst station is recommended in the Analyze phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>يمكن أن تكون المحطات ذات معدلات العيوب المنخفضة نماذج للممارسات الأفضل لتعميمها على خط الإنتاج.  •</t>
+          <t>محطة "Capping" لديها أعلى معدل عيوب: 4.54%.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>يُوصى بعمل رسم خرائط عملية أعمق لمحطة Capping لتحديد أوضاع الفشل المحددة.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>التباين على مستوى المحطة يؤكد أن حالة الآلة ومهارة المشغّل عوامل رئيسية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>المحطات ذات العيوب المنخفضة يمكن أن تكون نماذج للممارسات الأفضل.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>التركيز على محطة Capping هو الفرصة الأعلى تأثيراً للتحسين.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يُوصى برسم خرائط عملية مفصّلة للمحطة الأسوأ في مرحلة التحليل.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A horizontal bar chart ranking each production station by its defect rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Identifies which specific station in the production line is generating the most defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Longer bar = higher defect rate. The red line marks the overall average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Station-level stratification helps focus process improvement resources precisely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: A station with both high defects AND high downtime is a critical bottleneck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "4-Defect &amp; Quality" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = Station | Values = SUM(Units Defective) and SUM(Units Produced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Calculate Defect Rate per station: = Defective / Produced * 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Sort by Defect Rate descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Select Station + Defect Rate → Insert → Bar Chart (Horizontal/Clustered Bar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add a vertical average reference line using a secondary series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Color the highest bar red and others in a gradient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Add data labels and a chart title: "Defect Rate by Production Station".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -2888,146 +4627,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Measure Phase — Defect Rate by SKU</t>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Measure Phase — Defect Rate by SKU (Bottle Size)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>📈 Chart: Defect Rate by SKU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Defect Rate by SKU</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>📈  Chart: Defect Rate by SKU (Bottle Size)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>📊  Findings — Defect Rate by SKU (Bottle Size)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "1.5L" SKU has the highest defect rate at 4.53%, requiring immediate attention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Different bottle sizes show different defect profiles, suggesting that machine settings and tooling adjustments per SKU are inadequate.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The variation in defect rates across SKUs indicates that changeover quality and setup verification are inconsistent.</t>
+          <t xml:space="preserve">  •  "1.5L" SKU has the highest defect rate: 4.53%.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Improving SKU-specific quality control procedures and first-article inspection after changeover could reduce SKU-related defects.</t>
+          <t xml:space="preserve">  •  Different bottle sizes show different defect profiles — machine settings per SKU are inadequate.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The 1.5L SKU should be included as a key stratification variable in the Analyze phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Changeover quality and setup verification are inconsistent across SKUs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  The 1.5L SKU should be a key stratification variable in the Analyze phase.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>حجم المنتج "1.5L" لديه أعلى معدل عيوب بنسبة 4.53%، مما يستدعي اهتماماً فورياً.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>تُظهر أحجام الزجاجات المختلفة أنماط عيوب مختلفة، مما يشير إلى عدم كفاية ضبط الآلات والأدوات لكل حجم.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>التباين في معدلات العيوب عبر الأحجام يدل على عدم اتساق جودة التحويل والتحقق من الإعداد.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  SKU-specific first-article inspection after changeover is recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>تحسين إجراءات ضبط الجودة الخاصة بكل حجم وفحص المنتج الأول بعد التحويل يمكن أن يُقلل من عيوب الحجم.  •</t>
+          <t>حجم "1.5L" لديه أعلى معدل عيوب: 4.53%.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
+          <t>أحجام الزجاجات المختلفة تُظهر أنماط عيوب مختلفة — ضبط الآلات لكل حجم غير كافٍ.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>جودة التحويل والتحقق من الإعداد غير متسقة عبر الأحجام.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>يجب تضمين حجم 1.5L كمتغير تصنيف رئيسي في مرحلة التحليل.  •</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="8" customHeight="1"/>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يُوصى بفحص المنتج الأول بعد كل تحويل لكل حجم.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A bar chart comparing defect rates across different SKUs (330ml, 500ml, 1.5L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: SKU-level analysis reveals whether specific product sizes are more prone to defects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Each bar is a bottle size. Higher bar = more defects for that size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Helps identify if the defect problem is universal or SKU-specific.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: SKU-specific defects often point to changeover quality or machine calibration issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "4-Defect &amp; Quality" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = SKU | Values = SUM(Units Defective) and SUM(Units Produced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Calculate Defect Rate per SKU: = Defective / Produced * 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select SKU + Defect Rate → Insert → Clustered Column Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Add a horizontal reference line at the overall average defect rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add data labels showing the exact percentage on each bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Color the highest bar red to highlight the worst SKU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Defect Rate by SKU (Bottle Size)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3039,146 +4919,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Measure Phase — Pareto: Downtime Reasons</t>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Measure Phase — Pareto Chart — Downtime by Reason</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>📈 Chart: Pareto: Downtime Reasons</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Pareto: Downtime Reasons</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>📈  Chart: Pareto Chart — Downtime by Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>📊  Findings — Pareto Chart — Downtime by Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The top downtime cause is "SKU changeover" contributing 20.6% of all downtime minutes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The second cause is "Planned maintenance" at 12.9% of total downtime.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The top 3 downtime reasons account for 42.5% of all downtime — a clear Pareto concentration.</t>
+          <t xml:space="preserve">  •  Top downtime cause: "SKU changeover" = 20.6% of all downtime.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Addressing the top 3 causes alone could recover 43% of lost production time.</t>
+          <t xml:space="preserve">  •  2nd cause: "Planned maintenance" = 12.9% of total downtime.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • These top causes should be the primary targets for the Improve phase action plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Top 3 reasons account for 42.5% of all downtime — clear Pareto concentration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Addressing top 3 causes could recover 43% of lost production time.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>أكبر سبب للتوقف هو "SKU changeover" بنسبة 20.6% من إجمالي دقائق التوقف.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>السبب الثاني هو "Planned maintenance" بنسبة 12.9% من إجمالي التوقف.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>أعلى 3 أسباب للتوقف تمثل 42.5% من إجمالي التوقف — تركّز واضح وفق مبدأ باريتو.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  These causes should be primary targets for the Improve phase action plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>معالجة الأسباب الثلاثة الأولى وحدها يمكن أن يستعيد 43% من وقت الإنتاج الضائع.  •</t>
+          <t>أكبر سبب للتوقف: "SKU changeover" = 20.6% من إجمالي التوقف.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>يجب أن تكون هذه الأسباب الأولى الأهداف الرئيسية لخطة عمل مرحلة التحسين.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>السبب الثاني: "Planned maintenance" = 12.9% من إجمالي التوقف.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>أعلى 3 أسباب = 42.5% من إجمالي التوقف — تركّز واضح وفق باريتو.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>معالجة الأسباب الثلاثة الأولى يمكن أن يستعيد 43% من وقت الإنتاج الضائع.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يجب أن تكون هذه الأسباب الأهداف الرئيسية لخطة عمل مرحلة التحسين.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A Pareto chart of downtime minutes sorted by root cause/reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Identifies which downtime reasons are consuming the most production time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Bars = total downtime minutes per reason. Line = cumulative % of total downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Focuses maintenance and engineering efforts on the highest-impact downtime causes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: Eliminating the top 2-3 reasons can recover the majority of lost production capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "2-Downtime &amp; Stoppages" → create a summary: Reason | Total Duration (min).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Use SUMIF: =SUMIF(Reason_column, "Reason Name", Duration_column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Sort by Total Duration descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Add Cumulative % column: =SUM($B$2:B2)/SUM($B$2:$B$10)*100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Select Reason + Duration → Insert → Clustered Bar Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Add Cumulative % as a second series → Change to Line → Secondary Axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add 80% reference line on secondary axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Format bars in orange gradient, line in dark red. Add data labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3190,146 +5211,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Measure Phase — Downtime by Station</t>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Measure Phase — Downtime by Production Station</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>📈 Chart: Downtime by Station</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Downtime by Station</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>📈  Chart: Downtime by Production Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>📊  Findings — Downtime by Production Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The "Filling" station accounts for 22.5% of all downtime — the single largest contributor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • This aligns with the defect analysis, confirming that this station is the primary process bottleneck.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Stations with high downtime AND high defect rates should be treated as critical failure points requiring immediate intervention.</t>
+          <t xml:space="preserve">  •  "Filling" station = 22.5% of all downtime — the single largest contributor.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • A dedicated maintenance and process improvement plan for the top downtime stations is recommended.</t>
+          <t xml:space="preserve">  •  This aligns with defect analysis — confirming this station is the primary bottleneck.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Downtime distribution across stations should be monitored monthly as a leading indicator of process health.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Stations with high downtime AND high defects need immediate intervention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  A dedicated maintenance plan for top downtime stations is recommended.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>محطة "Filling" تمثل 22.5% من إجمالي التوقف — أكبر مساهم منفرد.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>هذا يتوافق مع تحليل العيوب، مما يؤكد أن هذه المحطة هي الاختناق الرئيسي في العملية.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>يجب التعامل مع المحطات ذات التوقف العالي ومعدلات العيوب العالية كنقاط فشل حرجة تستدعي تدخلاً فورياً.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Monthly downtime by station should be tracked as a leading process health indicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>يُوصى بخطة صيانة وتحسين عملية مخصصة لمحطات التوقف الأعلى.  •</t>
+          <t>محطة "Filling" = 22.5% من إجمالي التوقف — أكبر مساهم منفرد.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>يجب مراقبة توزيع التوقف عبر المحطات شهرياً كمؤشر قيادي لصحة العملية.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>هذا يتوافق مع تحليل العيوب — مما يؤكد أن هذه المحطة هي الاختناق الرئيسي.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>المحطات ذات التوقف العالي والعيوب العالية تحتاج تدخلاً فورياً.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>يُوصى بخطة صيانة مخصصة لمحطات التوقف الأعلى.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>يجب تتبع التوقف الشهري لكل محطة كمؤشر قيادي لصحة العملية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A bar chart showing total downtime minutes accumulated at each production station.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Pinpoints which physical location in the production line is causing the most stoppages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: Taller bar = more downtime at that station. Compare with defect rate by station.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Cross-referencing downtime and defect data by station identifies critical bottlenecks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: A station appearing in both top-defect and top-downtime charts is the highest priority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "2-Downtime &amp; Stoppages" → create a Pivot Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Set Rows = Station | Values = SUM(Duration (min)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Sort by total downtime descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select Station + Total Downtime → Insert → Clustered Column Chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Add a % of total label: calculate each station's share of total downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Color the highest bar in red/orange to highlight the worst station.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add data labels showing total minutes and % of total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Title: "Total Downtime by Production Station (minutes)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3341,146 +5503,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B39"/>
+  <dimension ref="B1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Measure Phase — Planned vs Unplanned Downtime</t>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Measure Phase — Planned vs. Unplanned Downtime</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Water Bottling Company | 6-Month Analysis: Nov 2025 – Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>📈 Chart: Planned vs Unplanned Downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>📊 Findings — Planned vs Unplanned Downtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+          <t>Water Bottling Company  |  6-Month Analysis: Nov 2025 – Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>📈  Chart: Planned vs. Unplanned Downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="6" customHeight="1">
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>📊  Findings — Planned vs. Unplanned Downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>🇬🇧  Key Findings (English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Unplanned downtime represents 55.3% of all downtime — more than 2.5x the 20% target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • This high proportion of unplanned stoppages indicates reactive maintenance dominates over preventive maintenance.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Unplanned downtime is the most disruptive type as it interrupts production schedules without warning.</t>
+          <t xml:space="preserve">  •  Unplanned downtime = 55.3% of all downtime — target is ≤20%.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The ratio of corrective to preventive maintenance events is 1175:1123, confirming a reactive maintenance culture.</t>
+          <t xml:space="preserve">  •  High unplanned downtime indicates reactive (not preventive) maintenance dominates.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Shifting to a proactive PM (Preventive Maintenance) strategy is critical to reducing unplanned downtime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>🇸🇦  النتائج الرئيسية (عربي)</t>
+          <t xml:space="preserve">  •  Unplanned stoppages interrupt schedules without warning — highest disruption type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Corrective vs. Preventive maintenance ratio: 1175:1123 — reactive culture confirmed.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>التوقف غير المخطط يمثل 55.3% من إجمالي التوقف — أكثر من 2.5 مرة من هدف 20%.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>هذه النسبة العالية من التوقفات غير المخططة تدل على هيمنة الصيانة التفاعلية على الصيانة الوقائية.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>التوقف غير المخطط هو الأكثر تدميراً لأنه يقاطع جداول الإنتاج دون إنذار مسبق.  •</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Shifting to proactive PM strategy is critical to reducing unplanned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>النتائج الرئيسية (عربي)  🇸🇦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>نسبة أوامر الصيانة التصحيحية إلى الوقائية 1175:1123، مما يؤكد ثقافة الصيانة التفاعلية.  •</t>
+          <t>التوقف غير المخطط = 55.3% من إجمالي التوقف — الهدف ≤20%.  •</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>التحول إلى استراتيجية الصيانة الوقائية الاستباقية أمر بالغ الأهمية لتقليل التوقف غير المخطط.  •</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="8" customHeight="1"/>
+          <t>التوقف غير المخطط المرتفع يدل على هيمنة الصيانة التفاعلية على الوقائية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>التوقفات غير المخططة تقاطع الجداول دون إنذار — أعلى نوع من حيث التعطيل.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>نسبة الصيانة التصحيحية إلى الوقائية: 1175:1123 — ثقافة تفاعلية مؤكدة.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>التحول إلى استراتيجية الصيانة الوقائية الاستباقية أمر بالغ الأهمية.  •</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1">
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>🔍  Chart Explanation — What This Chart Tells You</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Understanding the chart type, purpose, and how to interpret it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  What: A pie or stacked bar chart splitting downtime into Planned vs. Unplanned categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Why: Shows whether the organization controls its downtime (planned) or is controlled by it (unplanned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  How to read: The larger the unplanned slice, the more reactive the maintenance culture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Six Sigma use: Establishes the baseline for maintenance effectiveness in the Measure phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▸  Key insight: World-class manufacturing targets &lt;20% unplanned downtime. Above 50% is critical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="6" customHeight="1">
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>🛠️  How to Create This Chart in Excel — Step by Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Follow these steps to recreate this chart from the raw dataset:</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open "2-Downtime &amp; Stoppages" → filter by Type column (Planned / Unplanned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Use SUMIF: =SUMIF(Type_column,"Planned",Duration_column) and same for "Unplanned".</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Create a 2-row summary table: Type | Total Minutes | % of Total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Select Type + Total Minutes → Insert → Pie Chart (2-D Pie).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Alternatively, use a 100% Stacked Bar Chart for a cleaner look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Color: Planned = blue/green, Unplanned = red/orange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Add data labels showing both the value and percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Add a text box noting the 20% target for unplanned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="6" customHeight="1">
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B32"/>
-    <mergeCell ref="B35"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="B29"/>
-    <mergeCell ref="B33"/>
-    <mergeCell ref="B39"/>
-    <mergeCell ref="B38"/>
-    <mergeCell ref="B34"/>
-    <mergeCell ref="B28"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B36"/>
-    <mergeCell ref="B37"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="B27"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
